--- a/upload/plano_execucao_emendas_pix.xlsx
+++ b/upload/plano_execucao_emendas_pix.xlsx
@@ -2950,7 +2950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2969,6 +2969,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3375,7 +3376,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" ht="15">
+    <row r="2" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A2" s="4">
         <v>33145</v>
       </c>
@@ -3435,7 +3436,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="15">
+    <row r="3" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A3" s="4">
         <v>33145</v>
       </c>
@@ -3495,7 +3496,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="15">
+    <row r="4" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A4" s="4">
         <v>41913</v>
       </c>
@@ -3555,7 +3556,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="15">
+    <row r="5" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A5" s="4">
         <v>66441</v>
       </c>
@@ -3615,7 +3616,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="15">
+    <row r="6" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A6" s="4">
         <v>3498</v>
       </c>
@@ -3675,7 +3676,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="15">
+    <row r="7" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A7" s="4">
         <v>3498</v>
       </c>
@@ -3735,7 +3736,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="15">
+    <row r="8" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A8" s="4">
         <v>3498</v>
       </c>
@@ -3795,7 +3796,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="15">
+    <row r="9" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A9" s="4">
         <v>3498</v>
       </c>
@@ -3855,7 +3856,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="15">
+    <row r="10" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A10" s="4">
         <v>3952</v>
       </c>
@@ -3915,7 +3916,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="15">
+    <row r="11" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A11" s="4">
         <v>3952</v>
       </c>
@@ -3975,7 +3976,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="15">
+    <row r="12" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A12" s="4">
         <v>4464</v>
       </c>
@@ -4035,7 +4036,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="15">
+    <row r="13" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A13" s="4">
         <v>9300</v>
       </c>
@@ -4095,7 +4096,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26" ht="15">
+    <row r="14" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A14" s="4">
         <v>9734</v>
       </c>
@@ -4155,7 +4156,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="15">
+    <row r="15" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A15" s="4">
         <v>9846</v>
       </c>
@@ -4215,7 +4216,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26" ht="15">
+    <row r="16" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A16" s="4">
         <v>9848</v>
       </c>
@@ -4275,7 +4276,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="15">
+    <row r="17" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A17" s="4">
         <v>9864</v>
       </c>
@@ -4335,7 +4336,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="15">
+    <row r="18" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A18" s="4">
         <v>10213</v>
       </c>
@@ -4395,7 +4396,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="15">
+    <row r="19" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A19" s="4">
         <v>10624</v>
       </c>
@@ -4455,7 +4456,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="15">
+    <row r="20" spans="1:26" s="8" customFormat="1" ht="15">
       <c r="A20" s="4">
         <v>10670</v>
       </c>
@@ -4515,7 +4516,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1">
+    <row r="21" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A21" s="4">
         <v>10671</v>
       </c>
@@ -4575,7 +4576,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1">
+    <row r="22" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="4">
         <v>10671</v>
       </c>
@@ -4635,7 +4636,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1">
+    <row r="23" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="4">
         <v>10672</v>
       </c>
@@ -4695,7 +4696,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="4">
         <v>11332</v>
       </c>
@@ -4755,7 +4756,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="4">
         <v>11350</v>
       </c>
@@ -4815,7 +4816,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="4">
         <v>11351</v>
       </c>
@@ -4875,7 +4876,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="4">
         <v>11597</v>
       </c>
@@ -4935,7 +4936,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1">
+    <row r="28" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A28" s="4">
         <v>11597</v>
       </c>
@@ -4995,7 +4996,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1">
+    <row r="29" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="4">
         <v>11597</v>
       </c>
@@ -5055,7 +5056,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1">
+    <row r="30" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="4">
         <v>11781</v>
       </c>
@@ -5115,7 +5116,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A31" s="4">
         <v>11781</v>
       </c>
@@ -5175,7 +5176,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="4">
         <v>11890</v>
       </c>
@@ -5235,7 +5236,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1">
+    <row r="33" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A33" s="4">
         <v>11930</v>
       </c>
@@ -5295,7 +5296,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="4">
         <v>11930</v>
       </c>
@@ -5355,7 +5356,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="4">
         <v>11930</v>
       </c>
@@ -5415,7 +5416,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="4">
         <v>11930</v>
       </c>
@@ -5475,7 +5476,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="4">
         <v>11930</v>
       </c>
@@ -5535,7 +5536,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1">
+    <row r="38" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="4">
         <v>12157</v>
       </c>
@@ -5595,7 +5596,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1">
+    <row r="39" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A39" s="4">
         <v>12743</v>
       </c>
@@ -5655,7 +5656,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1">
+    <row r="40" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A40" s="4">
         <v>12873</v>
       </c>
@@ -5715,7 +5716,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1">
+    <row r="41" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A41" s="4">
         <v>13017</v>
       </c>
@@ -5775,7 +5776,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1">
+    <row r="42" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A42" s="4">
         <v>13023</v>
       </c>
@@ -5835,7 +5836,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1">
+    <row r="43" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A43" s="4">
         <v>13023</v>
       </c>
@@ -5895,7 +5896,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A44" s="4">
         <v>13196</v>
       </c>
@@ -5955,7 +5956,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1">
+    <row r="45" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A45" s="4">
         <v>13197</v>
       </c>
@@ -6015,7 +6016,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A46" s="4">
         <v>13287</v>
       </c>
@@ -6075,7 +6076,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1">
+    <row r="47" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A47" s="4">
         <v>13287</v>
       </c>
@@ -6135,7 +6136,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1">
+    <row r="48" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A48" s="4">
         <v>13670</v>
       </c>
@@ -6195,7 +6196,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1">
+    <row r="49" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A49" s="4">
         <v>13756</v>
       </c>
@@ -6255,7 +6256,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1">
+    <row r="50" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A50" s="4">
         <v>13790</v>
       </c>
@@ -6315,7 +6316,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" customHeight="1">
+    <row r="51" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A51" s="4">
         <v>13843</v>
       </c>
@@ -6375,7 +6376,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" ht="15.75" customHeight="1">
+    <row r="52" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A52" s="4">
         <v>13844</v>
       </c>
@@ -6435,7 +6436,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A53" s="4">
         <v>15696</v>
       </c>
@@ -6495,7 +6496,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A54" s="4">
         <v>15696</v>
       </c>
@@ -6555,7 +6556,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A55" s="4">
         <v>15777</v>
       </c>
@@ -6615,7 +6616,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A56" s="4">
         <v>15777</v>
       </c>
@@ -6675,7 +6676,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A57" s="4">
         <v>15804</v>
       </c>
@@ -6735,7 +6736,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A58" s="4">
         <v>16056</v>
       </c>
@@ -6795,7 +6796,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A59" s="4">
         <v>16238</v>
       </c>
@@ -6855,7 +6856,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A60" s="4">
         <v>16303</v>
       </c>
@@ -6915,7 +6916,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" spans="1:26" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A61" s="4">
         <v>16507</v>
       </c>
@@ -6975,7 +6976,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A62" s="4">
         <v>16507</v>
       </c>
@@ -7035,7 +7036,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" spans="1:26" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A63" s="4">
         <v>16507</v>
       </c>
@@ -7095,7 +7096,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" spans="1:26" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A64" s="4">
         <v>16507</v>
       </c>
@@ -7155,7 +7156,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" spans="1:26" ht="15.75" customHeight="1">
+    <row r="65" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A65" s="4">
         <v>16507</v>
       </c>
@@ -7215,7 +7216,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="15.75" customHeight="1">
+    <row r="66" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A66" s="4">
         <v>16886</v>
       </c>
@@ -7275,7 +7276,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" spans="1:26" ht="15.75" customHeight="1">
+    <row r="67" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A67" s="4">
         <v>16886</v>
       </c>
@@ -7335,7 +7336,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="15.75" customHeight="1">
+    <row r="68" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A68" s="4">
         <v>16978</v>
       </c>
@@ -7395,7 +7396,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" spans="1:26" ht="15.75" customHeight="1">
+    <row r="69" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A69" s="4">
         <v>17947</v>
       </c>
@@ -7455,7 +7456,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="15.75" customHeight="1">
+    <row r="70" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A70" s="4">
         <v>17947</v>
       </c>
@@ -7515,7 +7516,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A71" s="4">
         <v>18524</v>
       </c>
@@ -7575,7 +7576,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A72" s="4">
         <v>19136</v>
       </c>
@@ -7635,7 +7636,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" spans="1:26" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A73" s="4">
         <v>19136</v>
       </c>
@@ -7695,7 +7696,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A74" s="4">
         <v>19136</v>
       </c>
@@ -7755,7 +7756,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" spans="1:26" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A75" s="4">
         <v>19242</v>
       </c>
@@ -7815,7 +7816,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="15.75" customHeight="1">
+    <row r="76" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A76" s="4">
         <v>19776</v>
       </c>
@@ -7875,7 +7876,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" spans="1:26" ht="15.75" customHeight="1">
+    <row r="77" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A77" s="4">
         <v>19941</v>
       </c>
@@ -7935,7 +7936,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" spans="1:26" ht="15.75" customHeight="1">
+    <row r="78" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A78" s="4">
         <v>20106</v>
       </c>
@@ -7995,7 +7996,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" customHeight="1">
+    <row r="79" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A79" s="4">
         <v>20106</v>
       </c>
@@ -8055,7 +8056,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="15.75" customHeight="1">
+    <row r="80" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A80" s="4">
         <v>20140</v>
       </c>
@@ -8115,7 +8116,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" customHeight="1">
+    <row r="81" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A81" s="4">
         <v>20210</v>
       </c>
@@ -8175,7 +8176,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1">
+    <row r="82" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A82" s="4">
         <v>20452</v>
       </c>
@@ -8235,7 +8236,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1">
+    <row r="83" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A83" s="4">
         <v>21144</v>
       </c>
@@ -8295,7 +8296,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1">
+    <row r="84" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A84" s="4">
         <v>21247</v>
       </c>
@@ -8355,7 +8356,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1">
+    <row r="85" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A85" s="4">
         <v>21548</v>
       </c>
@@ -8415,7 +8416,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="15.75" customHeight="1">
+    <row r="86" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A86" s="4">
         <v>21692</v>
       </c>
@@ -8475,7 +8476,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" spans="1:26" ht="15.75" customHeight="1">
+    <row r="87" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A87" s="4">
         <v>22036</v>
       </c>
@@ -8535,7 +8536,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" customHeight="1">
+    <row r="88" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A88" s="4">
         <v>22061</v>
       </c>
@@ -8595,7 +8596,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1">
+    <row r="89" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A89" s="4">
         <v>22062</v>
       </c>
@@ -8655,7 +8656,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1">
+    <row r="90" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A90" s="4">
         <v>30956</v>
       </c>
@@ -8715,7 +8716,7 @@
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1">
+    <row r="91" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A91" s="4">
         <v>32765</v>
       </c>
@@ -8775,7 +8776,7 @@
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
     </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1">
+    <row r="92" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A92" s="4">
         <v>32765</v>
       </c>
@@ -8835,7 +8836,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1">
+    <row r="93" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A93" s="4">
         <v>33118</v>
       </c>
@@ -8895,7 +8896,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1">
+    <row r="94" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A94" s="4">
         <v>33385</v>
       </c>
@@ -8955,7 +8956,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1">
+    <row r="95" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A95" s="4">
         <v>33548</v>
       </c>
@@ -9015,7 +9016,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1">
+    <row r="96" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A96" s="4">
         <v>33573</v>
       </c>
@@ -9075,7 +9076,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" customHeight="1">
+    <row r="97" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A97" s="4">
         <v>33573</v>
       </c>
@@ -9135,7 +9136,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" customHeight="1">
+    <row r="98" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A98" s="4">
         <v>33775</v>
       </c>
@@ -9195,7 +9196,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1">
+    <row r="99" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A99" s="4">
         <v>33775</v>
       </c>
@@ -9255,7 +9256,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="15.75" customHeight="1">
+    <row r="100" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A100" s="4">
         <v>34009</v>
       </c>
@@ -9315,7 +9316,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1">
+    <row r="101" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A101" s="4">
         <v>34009</v>
       </c>
@@ -9375,7 +9376,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1">
+    <row r="102" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A102" s="4">
         <v>34026</v>
       </c>
@@ -9435,7 +9436,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1">
+    <row r="103" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A103" s="4">
         <v>35017</v>
       </c>
@@ -9495,7 +9496,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" ht="15.75" customHeight="1">
+    <row r="104" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A104" s="4">
         <v>37341</v>
       </c>
@@ -9555,7 +9556,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1">
+    <row r="105" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A105" s="4">
         <v>37341</v>
       </c>
@@ -9615,7 +9616,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1">
+    <row r="106" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A106" s="4">
         <v>37560</v>
       </c>
@@ -9675,7 +9676,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1">
+    <row r="107" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A107" s="4">
         <v>37560</v>
       </c>
@@ -9735,7 +9736,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" ht="15.75" customHeight="1">
+    <row r="108" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A108" s="4">
         <v>38065</v>
       </c>
@@ -9795,7 +9796,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" spans="1:26" ht="15.75" customHeight="1">
+    <row r="109" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A109" s="4">
         <v>38065</v>
       </c>
@@ -9855,7 +9856,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1">
+    <row r="110" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A110" s="4">
         <v>38065</v>
       </c>
@@ -9915,7 +9916,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1">
+    <row r="111" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A111" s="4">
         <v>38277</v>
       </c>
@@ -9975,7 +9976,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1">
+    <row r="112" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A112" s="4">
         <v>38440</v>
       </c>
@@ -10035,7 +10036,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" spans="1:26" ht="15.75" customHeight="1">
+    <row r="113" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A113" s="4">
         <v>41713</v>
       </c>
@@ -10095,7 +10096,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A114" s="4">
         <v>41759</v>
       </c>
@@ -10155,7 +10156,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" spans="1:26" ht="15.75" customHeight="1">
+    <row r="115" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A115" s="4">
         <v>41759</v>
       </c>
@@ -10215,7 +10216,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1">
+    <row r="116" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A116" s="4">
         <v>41759</v>
       </c>
@@ -10275,7 +10276,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1">
+    <row r="117" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A117" s="4">
         <v>41759</v>
       </c>
@@ -10335,7 +10336,7 @@
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
     </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1">
+    <row r="118" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A118" s="4">
         <v>41759</v>
       </c>
@@ -10395,7 +10396,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" spans="1:26" ht="15.75" customHeight="1">
+    <row r="119" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A119" s="4">
         <v>41914</v>
       </c>
@@ -10455,7 +10456,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="15.75" customHeight="1">
+    <row r="120" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A120" s="4">
         <v>41915</v>
       </c>
@@ -10515,7 +10516,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1">
+    <row r="121" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A121" s="4">
         <v>64894</v>
       </c>
@@ -10575,7 +10576,7 @@
       <c r="Y121" s="7"/>
       <c r="Z121" s="7"/>
     </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1">
+    <row r="122" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A122" s="4">
         <v>67738</v>
       </c>
@@ -10635,7 +10636,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1">
+    <row r="123" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A123" s="4">
         <v>67738</v>
       </c>
@@ -10695,7 +10696,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1">
+    <row r="124" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A124" s="4">
         <v>68122</v>
       </c>
@@ -10755,7 +10756,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1">
+    <row r="125" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A125" s="4">
         <v>68138</v>
       </c>
@@ -10815,7 +10816,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1">
+    <row r="126" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A126" s="4">
         <v>68138</v>
       </c>
@@ -10875,7 +10876,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1">
+    <row r="127" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A127" s="4">
         <v>68138</v>
       </c>
@@ -10935,7 +10936,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1">
+    <row r="128" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A128" s="4">
         <v>68237</v>
       </c>
@@ -10995,7 +10996,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" spans="1:26" ht="15.75" customHeight="1">
+    <row r="129" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A129" s="4">
         <v>69598</v>
       </c>
@@ -11055,7 +11056,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="15.75" customHeight="1">
+    <row r="130" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A130" s="4">
         <v>69633</v>
       </c>
@@ -11115,7 +11116,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" spans="1:26" ht="15.75" customHeight="1">
+    <row r="131" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="4">
         <v>69663</v>
       </c>
@@ -11175,7 +11176,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="15.75" customHeight="1">
+    <row r="132" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A132" s="4">
         <v>69862</v>
       </c>
@@ -11235,7 +11236,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" spans="1:26" ht="15.75" customHeight="1">
+    <row r="133" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A133" s="4">
         <v>69862</v>
       </c>
@@ -11295,7 +11296,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" spans="1:26" ht="15.75" customHeight="1">
+    <row r="134" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A134" s="4">
         <v>69869</v>
       </c>
@@ -11355,7 +11356,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" spans="1:26" ht="15.75" customHeight="1">
+    <row r="135" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A135" s="4">
         <v>69869</v>
       </c>
@@ -11415,7 +11416,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" ht="15.75" customHeight="1">
+    <row r="136" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A136" s="4">
         <v>69869</v>
       </c>
@@ -11475,7 +11476,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" spans="1:26" ht="15.75" customHeight="1">
+    <row r="137" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A137" s="4">
         <v>69901</v>
       </c>
@@ -11535,7 +11536,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" ht="15.75" customHeight="1">
+    <row r="138" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A138" s="4">
         <v>70095</v>
       </c>
@@ -11595,7 +11596,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" spans="1:26" ht="15.75" customHeight="1">
+    <row r="139" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A139" s="4">
         <v>70149</v>
       </c>
@@ -11655,7 +11656,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" ht="15.75" customHeight="1">
+    <row r="140" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A140" s="4">
         <v>70442</v>
       </c>
@@ -11715,7 +11716,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1">
+    <row r="141" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A141" s="4">
         <v>70442</v>
       </c>
@@ -11775,7 +11776,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" ht="15.75" customHeight="1">
+    <row r="142" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A142" s="4">
         <v>70442</v>
       </c>
@@ -11835,7 +11836,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" spans="1:26" ht="15.75" customHeight="1">
+    <row r="143" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A143" s="4">
         <v>70494</v>
       </c>
@@ -11895,7 +11896,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" ht="15.75" customHeight="1">
+    <row r="144" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A144" s="4">
         <v>71263</v>
       </c>
@@ -11955,7 +11956,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1">
+    <row r="145" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A145" s="4">
         <v>71443</v>
       </c>
@@ -12015,7 +12016,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" customHeight="1">
+    <row r="146" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A146" s="4">
         <v>71849</v>
       </c>
@@ -12075,7 +12076,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" spans="1:26" ht="15.75" customHeight="1">
+    <row r="147" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A147" s="4">
         <v>72393</v>
       </c>
@@ -12135,7 +12136,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="15.75" customHeight="1">
+    <row r="148" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A148" s="4">
         <v>72517</v>
       </c>
@@ -12195,7 +12196,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" spans="1:26" ht="15.75" customHeight="1">
+    <row r="149" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A149" s="4">
         <v>72968</v>
       </c>
@@ -12255,7 +12256,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="15.75" customHeight="1">
+    <row r="150" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A150" s="4">
         <v>72983</v>
       </c>
@@ -12315,7 +12316,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" customHeight="1">
+    <row r="151" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A151" s="4">
         <v>72983</v>
       </c>
@@ -12375,7 +12376,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" customHeight="1">
+    <row r="152" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A152" s="4">
         <v>72983</v>
       </c>
@@ -12435,7 +12436,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" customHeight="1">
+    <row r="153" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A153" s="4">
         <v>73106</v>
       </c>
@@ -12495,7 +12496,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" customHeight="1">
+    <row r="154" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A154" s="4">
         <v>73108</v>
       </c>
@@ -12555,7 +12556,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" customHeight="1">
+    <row r="155" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A155" s="4">
         <v>73108</v>
       </c>
@@ -12615,7 +12616,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1">
+    <row r="156" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A156" s="4">
         <v>74514</v>
       </c>
@@ -12675,7 +12676,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" customHeight="1">
+    <row r="157" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A157" s="4">
         <v>74514</v>
       </c>
@@ -12735,7 +12736,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1">
+    <row r="158" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A158" s="4">
         <v>74514</v>
       </c>
@@ -12795,7 +12796,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" customHeight="1">
+    <row r="159" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A159" s="4">
         <v>74980</v>
       </c>
@@ -12855,7 +12856,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" customHeight="1">
+    <row r="160" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A160" s="4">
         <v>77102</v>
       </c>
@@ -12913,7 +12914,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" customHeight="1">
+    <row r="161" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A161" s="4">
         <v>77230</v>
       </c>
@@ -12971,7 +12972,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" customHeight="1">
+    <row r="162" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A162" s="4">
         <v>77231</v>
       </c>
@@ -13029,7 +13030,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" customHeight="1">
+    <row r="163" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A163" s="4">
         <v>77229</v>
       </c>
@@ -13087,7 +13088,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" customHeight="1">
+    <row r="164" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A164" s="4">
         <v>78820</v>
       </c>
@@ -13145,7 +13146,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" customHeight="1">
+    <row r="165" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A165" s="4">
         <v>79085</v>
       </c>
@@ -13203,7 +13204,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" customHeight="1">
+    <row r="166" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A166" s="4">
         <v>79569</v>
       </c>
@@ -13261,7 +13262,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" customHeight="1">
+    <row r="167" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A167" s="4">
         <v>79571</v>
       </c>
@@ -13319,7 +13320,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1">
+    <row r="168" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A168" s="4">
         <v>79570</v>
       </c>
@@ -13377,7 +13378,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" spans="1:26" ht="15.75" customHeight="1">
+    <row r="169" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A169" s="4">
         <v>79702</v>
       </c>
@@ -13435,7 +13436,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" spans="1:26" ht="15.75" customHeight="1">
+    <row r="170" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A170" s="4">
         <v>79703</v>
       </c>
@@ -13493,7 +13494,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" spans="1:26" ht="15.75" customHeight="1">
+    <row r="171" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A171" s="4">
         <v>79701</v>
       </c>
@@ -13551,7 +13552,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" spans="1:26" ht="15.75" customHeight="1">
+    <row r="172" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A172" s="4">
         <v>79910</v>
       </c>
@@ -13609,7 +13610,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" spans="1:26" ht="15.75" customHeight="1">
+    <row r="173" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A173" s="4">
         <v>79911</v>
       </c>
@@ -13667,7 +13668,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" spans="1:26" ht="15.75" customHeight="1">
+    <row r="174" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A174" s="4">
         <v>79913</v>
       </c>
@@ -13725,7 +13726,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" spans="1:26" ht="15.75" customHeight="1">
+    <row r="175" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A175" s="4">
         <v>79909</v>
       </c>
@@ -13783,7 +13784,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" spans="1:26" ht="15.75" customHeight="1">
+    <row r="176" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A176" s="4">
         <v>79907</v>
       </c>
@@ -13841,7 +13842,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" spans="1:26" ht="15.75" customHeight="1">
+    <row r="177" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A177" s="4">
         <v>79912</v>
       </c>
@@ -13899,7 +13900,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" spans="1:26" ht="15.75" customHeight="1">
+    <row r="178" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A178" s="4">
         <v>80939</v>
       </c>
@@ -13957,7 +13958,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" spans="1:26" ht="15.75" customHeight="1">
+    <row r="179" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A179" s="4">
         <v>80938</v>
       </c>
@@ -14015,7 +14016,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" spans="1:26" ht="15.75" customHeight="1">
+    <row r="180" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A180" s="4">
         <v>81215</v>
       </c>
@@ -14073,7 +14074,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" customHeight="1">
+    <row r="181" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A181" s="4">
         <v>82114</v>
       </c>
@@ -14131,7 +14132,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" spans="1:26" ht="15.75" customHeight="1">
+    <row r="182" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A182" s="4">
         <v>82116</v>
       </c>
@@ -14189,7 +14190,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" spans="1:26" ht="15.75" customHeight="1">
+    <row r="183" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A183" s="4">
         <v>82115</v>
       </c>
@@ -14247,7 +14248,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" spans="1:26" ht="15.75" customHeight="1">
+    <row r="184" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A184" s="4">
         <v>82154</v>
       </c>
@@ -14305,7 +14306,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" spans="1:26" ht="15.75" customHeight="1">
+    <row r="185" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A185" s="4">
         <v>83081</v>
       </c>
@@ -14363,7 +14364,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" spans="1:26" ht="15.75" customHeight="1">
+    <row r="186" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A186" s="4">
         <v>83941</v>
       </c>
@@ -14421,7 +14422,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" spans="1:26" ht="15.75" customHeight="1">
+    <row r="187" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A187" s="4">
         <v>84771</v>
       </c>
@@ -14479,7 +14480,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" spans="1:26" ht="15.75" customHeight="1">
+    <row r="188" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A188" s="4">
         <v>84772</v>
       </c>
@@ -14537,7 +14538,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" spans="1:26" ht="15.75" customHeight="1">
+    <row r="189" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A189" s="4">
         <v>85244</v>
       </c>
@@ -14595,7 +14596,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" customHeight="1">
+    <row r="190" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A190" s="4">
         <v>85248</v>
       </c>
@@ -14653,7 +14654,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" customHeight="1">
+    <row r="191" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A191" s="4">
         <v>85241</v>
       </c>
@@ -14711,7 +14712,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" customHeight="1">
+    <row r="192" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A192" s="4">
         <v>85242</v>
       </c>
@@ -14769,7 +14770,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" spans="1:26" ht="15.75" customHeight="1">
+    <row r="193" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A193" s="4">
         <v>85247</v>
       </c>
@@ -14827,7 +14828,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" spans="1:26" ht="15.75" customHeight="1">
+    <row r="194" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A194" s="4">
         <v>85245</v>
       </c>
@@ -14885,7 +14886,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" spans="1:26" ht="15.75" customHeight="1">
+    <row r="195" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A195" s="4">
         <v>79906</v>
       </c>
@@ -14943,7 +14944,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" spans="1:26" ht="15.75" customHeight="1">
+    <row r="196" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A196" s="4">
         <v>79086</v>
       </c>
@@ -15001,7 +15002,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" spans="1:26" ht="15.75" customHeight="1">
+    <row r="197" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A197" s="4">
         <v>85243</v>
       </c>
@@ -15059,7 +15060,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" spans="1:26" ht="15.75" customHeight="1">
+    <row r="198" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A198" s="4">
         <v>79908</v>
       </c>
@@ -15117,7 +15118,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" spans="1:26" ht="15.75" customHeight="1">
+    <row r="199" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A199" s="4">
         <v>84775</v>
       </c>
@@ -15175,7 +15176,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" spans="1:26" ht="15.75" customHeight="1">
+    <row r="200" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A200" s="4">
         <v>79572</v>
       </c>
@@ -15233,7 +15234,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" spans="1:26" ht="15.75" customHeight="1">
+    <row r="201" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A201" s="4">
         <v>80781</v>
       </c>
@@ -15291,7 +15292,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" spans="1:26" ht="15.75" customHeight="1">
+    <row r="202" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A202" s="4">
         <v>84774</v>
       </c>
@@ -15349,7 +15350,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" spans="1:26" ht="15.75" customHeight="1">
+    <row r="203" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A203" s="4">
         <v>84774</v>
       </c>
@@ -15407,7 +15408,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" spans="1:26" ht="15.75" customHeight="1">
+    <row r="204" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A204" s="4">
         <v>77101</v>
       </c>
@@ -15465,7 +15466,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" spans="1:26" ht="15.75" customHeight="1">
+    <row r="205" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A205" s="4">
         <v>85249</v>
       </c>
@@ -15523,7 +15524,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" spans="1:26" ht="15.75" customHeight="1">
+    <row r="206" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A206" s="4">
         <v>85246</v>
       </c>
@@ -15581,7 +15582,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" spans="1:26" ht="15.75" customHeight="1">
+    <row r="207" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A207" s="4">
         <v>84773</v>
       </c>
@@ -15639,7 +15640,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" spans="1:26" ht="15.75" customHeight="1">
+    <row r="208" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A208" s="4">
         <v>87163</v>
       </c>
@@ -15697,7 +15698,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" customHeight="1">
+    <row r="209" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A209" s="4">
         <v>87164</v>
       </c>
@@ -15755,7 +15756,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" spans="1:26" ht="15.75" customHeight="1">
+    <row r="210" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A210" s="4">
         <v>88505</v>
       </c>
@@ -15813,7 +15814,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" spans="1:26" ht="15.75" customHeight="1">
+    <row r="211" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A211" s="4">
         <v>88504</v>
       </c>
@@ -15871,7 +15872,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" spans="1:26" ht="15.75" customHeight="1">
+    <row r="212" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A212" s="4">
         <v>88503</v>
       </c>
@@ -15929,7 +15930,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" spans="1:26" ht="15.75" customHeight="1">
+    <row r="213" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A213" s="4">
         <v>87282</v>
       </c>

--- a/upload/plano_execucao_emendas_pix.xlsx
+++ b/upload/plano_execucao_emendas_pix.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F87458-6543-4B0D-8585-9F2D33EF191C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="780" yWindow="720" windowWidth="19755" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -18,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2879,12 +2869,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="6" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2950,7 +2940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2968,8 +2958,7 @@
     <xf numFmtId="6" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3303,20 +3292,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z213"/>
-  <sheetFormatPr defaultColWidth="14.375" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="15.75" customWidth="1"/>
+    <col min="1" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
-    <col min="9" max="14" width="15.75" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" customWidth="1"/>
+    <col min="9" max="14" width="15.7109375" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="15.75" customWidth="1"/>
-    <col min="17" max="26" width="11.375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+    <col min="17" max="26" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>438</v>
       </c>
@@ -3376,7 +3365,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>33145</v>
       </c>
@@ -3436,7 +3425,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>33145</v>
       </c>
@@ -3496,7 +3485,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>41913</v>
       </c>
@@ -3556,7 +3545,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>66441</v>
       </c>
@@ -3616,7 +3605,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3498</v>
       </c>
@@ -3676,7 +3665,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>3498</v>
       </c>
@@ -3736,7 +3725,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>3498</v>
       </c>
@@ -3796,7 +3785,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>3498</v>
       </c>
@@ -3856,7 +3845,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>3952</v>
       </c>
@@ -3916,7 +3905,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>3952</v>
       </c>
@@ -3976,7 +3965,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>4464</v>
       </c>
@@ -4036,7 +4025,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>9300</v>
       </c>
@@ -4096,7 +4085,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>9734</v>
       </c>
@@ -4156,7 +4145,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>9846</v>
       </c>
@@ -4216,7 +4205,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>9848</v>
       </c>
@@ -4276,7 +4265,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>9864</v>
       </c>
@@ -4336,7 +4325,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>10213</v>
       </c>
@@ -4396,7 +4385,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>10624</v>
       </c>
@@ -4456,7 +4445,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26" s="8" customFormat="1" ht="15">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>10670</v>
       </c>
@@ -4516,7 +4505,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>10671</v>
       </c>
@@ -4576,7 +4565,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>10671</v>
       </c>
@@ -4636,7 +4625,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>10672</v>
       </c>
@@ -4696,7 +4685,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>11332</v>
       </c>
@@ -4756,7 +4745,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>11350</v>
       </c>
@@ -4816,7 +4805,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>11351</v>
       </c>
@@ -4876,7 +4865,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>11597</v>
       </c>
@@ -4936,7 +4925,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>11597</v>
       </c>
@@ -4996,7 +4985,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>11597</v>
       </c>
@@ -5056,7 +5045,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>11781</v>
       </c>
@@ -5116,7 +5105,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>11781</v>
       </c>
@@ -5176,7 +5165,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>11890</v>
       </c>
@@ -5236,7 +5225,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>11930</v>
       </c>
@@ -5296,7 +5285,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>11930</v>
       </c>
@@ -5356,7 +5345,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>11930</v>
       </c>
@@ -5416,7 +5405,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>11930</v>
       </c>
@@ -5476,7 +5465,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>11930</v>
       </c>
@@ -5536,7 +5525,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>12157</v>
       </c>
@@ -5596,7 +5585,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>12743</v>
       </c>
@@ -5656,7 +5645,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>12873</v>
       </c>
@@ -5716,7 +5705,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>13017</v>
       </c>
@@ -5776,7 +5765,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>13023</v>
       </c>
@@ -5836,7 +5825,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>13023</v>
       </c>
@@ -5896,7 +5885,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>13196</v>
       </c>
@@ -5956,7 +5945,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>13197</v>
       </c>
@@ -6016,7 +6005,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>13287</v>
       </c>
@@ -6076,7 +6065,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>13287</v>
       </c>
@@ -6136,7 +6125,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>13670</v>
       </c>
@@ -6196,7 +6185,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>13756</v>
       </c>
@@ -6256,7 +6245,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>13790</v>
       </c>
@@ -6316,7 +6305,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>13843</v>
       </c>
@@ -6376,7 +6365,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>13844</v>
       </c>
@@ -6436,7 +6425,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>15696</v>
       </c>
@@ -6496,7 +6485,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>15696</v>
       </c>
@@ -6556,7 +6545,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>15777</v>
       </c>
@@ -6616,7 +6605,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>15777</v>
       </c>
@@ -6676,7 +6665,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>15804</v>
       </c>
@@ -6736,7 +6725,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>16056</v>
       </c>
@@ -6796,7 +6785,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>16238</v>
       </c>
@@ -6856,7 +6845,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>16303</v>
       </c>
@@ -6916,7 +6905,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>16507</v>
       </c>
@@ -6976,7 +6965,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>16507</v>
       </c>
@@ -7036,7 +7025,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>16507</v>
       </c>
@@ -7096,7 +7085,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>16507</v>
       </c>
@@ -7156,7 +7145,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>16507</v>
       </c>
@@ -7216,7 +7205,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>16886</v>
       </c>
@@ -7276,7 +7265,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>16886</v>
       </c>
@@ -7336,7 +7325,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>16978</v>
       </c>
@@ -7396,7 +7385,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>17947</v>
       </c>
@@ -7456,7 +7445,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>17947</v>
       </c>
@@ -7516,7 +7505,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>18524</v>
       </c>
@@ -7576,7 +7565,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>19136</v>
       </c>
@@ -7636,7 +7625,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>19136</v>
       </c>
@@ -7696,7 +7685,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>19136</v>
       </c>
@@ -7756,7 +7745,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>19242</v>
       </c>
@@ -7816,7 +7805,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>19776</v>
       </c>
@@ -7876,7 +7865,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>19941</v>
       </c>
@@ -7936,7 +7925,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>20106</v>
       </c>
@@ -7996,7 +7985,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>20106</v>
       </c>
@@ -8056,7 +8045,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>20140</v>
       </c>
@@ -8116,7 +8105,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>20210</v>
       </c>
@@ -8176,7 +8165,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>20452</v>
       </c>
@@ -8236,7 +8225,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>21144</v>
       </c>
@@ -8296,7 +8285,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>21247</v>
       </c>
@@ -8356,7 +8345,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>21548</v>
       </c>
@@ -8416,7 +8405,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>21692</v>
       </c>
@@ -8476,7 +8465,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>22036</v>
       </c>
@@ -8536,7 +8525,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>22061</v>
       </c>
@@ -8596,7 +8585,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>22062</v>
       </c>
@@ -8656,7 +8645,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>30956</v>
       </c>
@@ -8716,7 +8705,7 @@
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
     </row>
-    <row r="91" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>32765</v>
       </c>
@@ -8776,7 +8765,7 @@
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
     </row>
-    <row r="92" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>32765</v>
       </c>
@@ -8836,7 +8825,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>33118</v>
       </c>
@@ -8896,7 +8885,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>33385</v>
       </c>
@@ -8956,7 +8945,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>33548</v>
       </c>
@@ -9016,7 +9005,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>33573</v>
       </c>
@@ -9076,7 +9065,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>33573</v>
       </c>
@@ -9136,7 +9125,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>33775</v>
       </c>
@@ -9196,7 +9185,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>33775</v>
       </c>
@@ -9256,7 +9245,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>34009</v>
       </c>
@@ -9316,7 +9305,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>34009</v>
       </c>
@@ -9376,7 +9365,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>34026</v>
       </c>
@@ -9436,7 +9425,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>35017</v>
       </c>
@@ -9496,7 +9485,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>37341</v>
       </c>
@@ -9556,7 +9545,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>37341</v>
       </c>
@@ -9616,7 +9605,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>37560</v>
       </c>
@@ -9676,7 +9665,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>37560</v>
       </c>
@@ -9736,7 +9725,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>38065</v>
       </c>
@@ -9796,7 +9785,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>38065</v>
       </c>
@@ -9856,7 +9845,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>38065</v>
       </c>
@@ -9916,7 +9905,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>38277</v>
       </c>
@@ -9976,7 +9965,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>38440</v>
       </c>
@@ -10036,7 +10025,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>41713</v>
       </c>
@@ -10096,7 +10085,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>41759</v>
       </c>
@@ -10156,7 +10145,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>41759</v>
       </c>
@@ -10216,7 +10205,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>41759</v>
       </c>
@@ -10276,7 +10265,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>41759</v>
       </c>
@@ -10336,7 +10325,7 @@
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
     </row>
-    <row r="118" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>41759</v>
       </c>
@@ -10396,7 +10385,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>41914</v>
       </c>
@@ -10456,7 +10445,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>41915</v>
       </c>
@@ -10516,7 +10505,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>64894</v>
       </c>
@@ -10576,7 +10565,7 @@
       <c r="Y121" s="7"/>
       <c r="Z121" s="7"/>
     </row>
-    <row r="122" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>67738</v>
       </c>
@@ -10636,7 +10625,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>67738</v>
       </c>
@@ -10696,7 +10685,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>68122</v>
       </c>
@@ -10756,7 +10745,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>68138</v>
       </c>
@@ -10816,7 +10805,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>68138</v>
       </c>
@@ -10876,7 +10865,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>68138</v>
       </c>
@@ -10936,7 +10925,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>68237</v>
       </c>
@@ -10996,7 +10985,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>69598</v>
       </c>
@@ -11056,7 +11045,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>69633</v>
       </c>
@@ -11116,7 +11105,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>69663</v>
       </c>
@@ -11176,7 +11165,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>69862</v>
       </c>
@@ -11236,7 +11225,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>69862</v>
       </c>
@@ -11296,7 +11285,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>69869</v>
       </c>
@@ -11356,7 +11345,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>69869</v>
       </c>
@@ -11416,7 +11405,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>69869</v>
       </c>
@@ -11476,7 +11465,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>69901</v>
       </c>
@@ -11536,7 +11525,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>70095</v>
       </c>
@@ -11596,7 +11585,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>70149</v>
       </c>
@@ -11656,7 +11645,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>70442</v>
       </c>
@@ -11716,7 +11705,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>70442</v>
       </c>
@@ -11776,7 +11765,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>70442</v>
       </c>
@@ -11836,7 +11825,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>70494</v>
       </c>
@@ -11896,7 +11885,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>71263</v>
       </c>
@@ -11956,7 +11945,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>71443</v>
       </c>
@@ -12016,7 +12005,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>71849</v>
       </c>
@@ -12076,7 +12065,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>72393</v>
       </c>
@@ -12136,7 +12125,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>72517</v>
       </c>
@@ -12196,7 +12185,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>72968</v>
       </c>
@@ -12256,7 +12245,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>72983</v>
       </c>
@@ -12316,7 +12305,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>72983</v>
       </c>
@@ -12376,7 +12365,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>72983</v>
       </c>
@@ -12436,7 +12425,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>73106</v>
       </c>
@@ -12496,7 +12485,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>73108</v>
       </c>
@@ -12556,7 +12545,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>73108</v>
       </c>
@@ -12616,7 +12605,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>74514</v>
       </c>
@@ -12676,7 +12665,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>74514</v>
       </c>
@@ -12736,7 +12725,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>74514</v>
       </c>
@@ -12796,7 +12785,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>74980</v>
       </c>
@@ -12856,7 +12845,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>77102</v>
       </c>
@@ -12914,7 +12903,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>77230</v>
       </c>
@@ -12972,7 +12961,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>77231</v>
       </c>
@@ -13030,7 +13019,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>77229</v>
       </c>
@@ -13088,7 +13077,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>78820</v>
       </c>
@@ -13146,7 +13135,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>79085</v>
       </c>
@@ -13204,7 +13193,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>79569</v>
       </c>
@@ -13262,7 +13251,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>79571</v>
       </c>
@@ -13320,7 +13309,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>79570</v>
       </c>
@@ -13378,7 +13367,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>79702</v>
       </c>
@@ -13436,7 +13425,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>79703</v>
       </c>
@@ -13494,7 +13483,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>79701</v>
       </c>
@@ -13552,7 +13541,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>79910</v>
       </c>
@@ -13610,7 +13599,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>79911</v>
       </c>
@@ -13668,7 +13657,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>79913</v>
       </c>
@@ -13726,7 +13715,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>79909</v>
       </c>
@@ -13784,7 +13773,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>79907</v>
       </c>
@@ -13842,7 +13831,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>79912</v>
       </c>
@@ -13900,7 +13889,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>80939</v>
       </c>
@@ -13958,7 +13947,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>80938</v>
       </c>
@@ -14016,7 +14005,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>81215</v>
       </c>
@@ -14074,7 +14063,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>82114</v>
       </c>
@@ -14132,7 +14121,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>82116</v>
       </c>
@@ -14190,7 +14179,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>82115</v>
       </c>
@@ -14248,7 +14237,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>82154</v>
       </c>
@@ -14306,7 +14295,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>83081</v>
       </c>
@@ -14364,7 +14353,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>83941</v>
       </c>
@@ -14422,7 +14411,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>84771</v>
       </c>
@@ -14480,7 +14469,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>84772</v>
       </c>
@@ -14538,7 +14527,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>85244</v>
       </c>
@@ -14596,7 +14585,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>85248</v>
       </c>
@@ -14654,7 +14643,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>85241</v>
       </c>
@@ -14712,7 +14701,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>85242</v>
       </c>
@@ -14770,7 +14759,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>85247</v>
       </c>
@@ -14828,7 +14817,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>85245</v>
       </c>
@@ -14886,7 +14875,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>79906</v>
       </c>
@@ -14944,7 +14933,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>79086</v>
       </c>
@@ -15002,7 +14991,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>85243</v>
       </c>
@@ -15060,7 +15049,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>79908</v>
       </c>
@@ -15118,7 +15107,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>84775</v>
       </c>
@@ -15176,7 +15165,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>79572</v>
       </c>
@@ -15234,7 +15223,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>80781</v>
       </c>
@@ -15292,7 +15281,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>84774</v>
       </c>
@@ -15350,7 +15339,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>84774</v>
       </c>
@@ -15408,7 +15397,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>77101</v>
       </c>
@@ -15466,7 +15455,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>85249</v>
       </c>
@@ -15524,7 +15513,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
         <v>85246</v>
       </c>
@@ -15582,7 +15571,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>84773</v>
       </c>
@@ -15640,7 +15629,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>87163</v>
       </c>
@@ -15698,7 +15687,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>87164</v>
       </c>
@@ -15756,7 +15745,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>88505</v>
       </c>
@@ -15814,7 +15803,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>88504</v>
       </c>
@@ -15872,7 +15861,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>88503</v>
       </c>
@@ -15930,7 +15919,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" spans="1:26" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>87282</v>
       </c>
